--- a/outputs/monitor_xlsx/20260323.xlsx
+++ b/outputs/monitor_xlsx/20260323.xlsx
@@ -544,10 +544,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.47%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-1.39%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-4.81%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.69%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+1.34%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-2.35%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-6.92%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-839.23億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-411.38億</t>
@@ -807,7 +769,6 @@
           <t>105.35億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>22.33億</t>
@@ -818,8 +779,6 @@
           <t>111.64億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>110.09%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>133.74%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-1044.99億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>10096口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11622口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>48.57億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-5.91億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2412,6 +2354,112 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7885</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>152</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>41</v>
+      </c>
+      <c r="J23" t="n">
+        <v>30</v>
+      </c>
+      <c r="K23" t="n">
+        <v>276</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1285</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8973</v>
+      </c>
+      <c r="N23" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3534</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1683</v>
+      </c>
+      <c r="H24" t="n">
+        <v>716</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J24" t="n">
+        <v>151</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2785</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12744</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106311</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260323.xlsx
+++ b/outputs/monitor_xlsx/20260323.xlsx
@@ -544,6 +544,10 @@
           <t>-2.45%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +570,10 @@
           <t>-3.47%</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>-1.39%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,14 +636,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4350.4$</t>
+          <t>4404.1$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-4.81%</t>
-        </is>
-      </c>
+          <t>-3.64%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>+0.69%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>+1.34%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>-2.35%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,14 +740,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>91.52$</t>
+          <t>88.13$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-6.92%</t>
-        </is>
-      </c>
+          <t>-10.36%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,6 +769,7 @@
           <t>-839.23億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-411.38億</t>
@@ -769,6 +807,7 @@
           <t>105.35億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>22.33億</t>
@@ -779,6 +818,8 @@
           <t>111.64億</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>110.09%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>133.74%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,6 +863,11 @@
           <t>-1044.99億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>10096口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11622口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,6 +911,7 @@
           <t>48.57億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-5.91億</t>
@@ -961,6 +1016,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1284,12 +1336,7 @@
       <c r="N4" t="n">
         <v>-4504837</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1344,12 +1391,7 @@
       <c r="N5" t="n">
         <v>-78845</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1404,12 +1446,7 @@
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1464,12 +1501,7 @@
       <c r="N7" t="n">
         <v>-6483121</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1478,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1492,44 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>107.5</v>
+        <v>1565</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-2.27</v>
+        <v>-2.8</v>
       </c>
       <c r="F8" t="n">
-        <v>148725</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>13049</v>
+        <v>3284</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>-27</v>
       </c>
       <c r="H8" t="n">
-        <v>-133816</v>
+        <v>1150</v>
       </c>
       <c r="I8" t="n">
-        <v>-5946</v>
+        <v>115</v>
       </c>
       <c r="J8" t="n">
-        <v>68470</v>
+        <v>226</v>
       </c>
       <c r="K8" t="n">
-        <v>3291</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>128498</v>
+        <v>2186</v>
       </c>
       <c r="M8" t="n">
-        <v>530662</v>
+        <v>8949</v>
       </c>
       <c r="N8" t="n">
-        <v>-1124745</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140175</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1538,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1552,44 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2795</v>
+        <v>1520</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-0.53</v>
+        <v>-4.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3517</v>
+        <v>3534</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-24</v>
+        <v>-51</v>
       </c>
       <c r="H9" t="n">
-        <v>-417</v>
+        <v>-1632</v>
       </c>
       <c r="I9" t="n">
-        <v>112</v>
+        <v>716</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>1306</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L9" t="n">
-        <v>2005</v>
+        <v>2785</v>
       </c>
       <c r="M9" t="n">
-        <v>7691</v>
+        <v>13423</v>
       </c>
       <c r="N9" t="n">
-        <v>-89580</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106311</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1598,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1612,44 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3190</v>
+        <v>2795</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-5.48</v>
+        <v>-0.53</v>
       </c>
       <c r="F10" t="n">
-        <v>1597</v>
+        <v>3517</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-502</v>
+        <v>-24</v>
       </c>
       <c r="H10" t="n">
-        <v>1166</v>
+        <v>-417</v>
       </c>
       <c r="I10" t="n">
-        <v>-8</v>
+        <v>112</v>
       </c>
       <c r="J10" t="n">
-        <v>-306</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L10" t="n">
-        <v>5913</v>
+        <v>2005</v>
       </c>
       <c r="M10" t="n">
-        <v>23107</v>
+        <v>7691</v>
       </c>
       <c r="N10" t="n">
-        <v>-19782</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89580</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1704,12 +1721,7 @@
       <c r="N11" t="n">
         <v>-19518</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1718,58 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1480</v>
+        <v>7885</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-9.76</v>
+        <v>-0.57</v>
       </c>
       <c r="F12" t="n">
-        <v>795</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-205</v>
+        <v>658</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>432</v>
+        <v>152</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="J12" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
-        <v>-76</v>
+        <v>276</v>
       </c>
       <c r="M12" t="n">
-        <v>-616</v>
+        <v>1009</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8973</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1778,12 +1785,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1792,44 +1799,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>380</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-6.06</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>21965</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-232</v>
+        <v>-205</v>
       </c>
       <c r="H13" t="n">
-        <v>-4621</v>
+        <v>432</v>
       </c>
       <c r="I13" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>-2416</v>
+        <v>63</v>
       </c>
       <c r="K13" t="n">
-        <v>-103</v>
+        <v>65</v>
       </c>
       <c r="L13" t="n">
-        <v>-399</v>
+        <v>-76</v>
       </c>
       <c r="M13" t="n">
-        <v>2050</v>
+        <v>-616</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1838,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1852,41 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-8.970000000000001</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>625</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>4</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>-232</v>
       </c>
       <c r="H14" t="n">
-        <v>-30</v>
+        <v>-4621</v>
+      </c>
+      <c r="I14" t="n">
+        <v>167</v>
       </c>
       <c r="J14" t="n">
-        <v>28</v>
+        <v>-2416</v>
       </c>
       <c r="K14" t="n">
-        <v>-54</v>
+        <v>-103</v>
       </c>
       <c r="L14" t="n">
-        <v>-21</v>
+        <v>-399</v>
       </c>
       <c r="M14" t="n">
-        <v>-82</v>
+        <v>2050</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1895,58 +1895,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1565</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-2.8</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>3284</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-27</v>
+        <v>-1620</v>
       </c>
       <c r="H15" t="n">
-        <v>1150</v>
+        <v>-15</v>
       </c>
       <c r="I15" t="n">
-        <v>115</v>
+        <v>1512</v>
       </c>
       <c r="J15" t="n">
-        <v>226</v>
+        <v>806</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>2186</v>
+        <v>26</v>
       </c>
       <c r="M15" t="n">
-        <v>8949</v>
+        <v>866</v>
       </c>
       <c r="N15" t="n">
-        <v>-140175</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1955,12 +1950,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1969,497 +1964,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>821</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-9.98</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1081</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>-169</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>44</v>
       </c>
       <c r="H16" t="n">
-        <v>-2449</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>404</v>
+        <v>-6</v>
       </c>
       <c r="K16" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L16" t="n">
-        <v>-139</v>
+        <v>-104</v>
       </c>
       <c r="M16" t="n">
-        <v>-39</v>
+        <v>176</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>915</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2947</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-602</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-4965</v>
-      </c>
-      <c r="I17" t="n">
-        <v>55</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-1530</v>
-      </c>
-      <c r="K17" t="n">
-        <v>226</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3039</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11099</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-47645</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1120</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1167</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="H18" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M18" t="n">
-        <v>176</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>830</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F19" t="n">
-        <v>13680</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-1620</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1512</v>
-      </c>
-      <c r="J19" t="n">
-        <v>806</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>26</v>
-      </c>
-      <c r="M19" t="n">
-        <v>866</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>241.5</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-5.48</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3598</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="H20" t="n">
-        <v>149</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K20" t="n">
-        <v>160</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6300</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28039</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-59054</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21417</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1580</v>
-      </c>
-      <c r="J21" t="n">
-        <v>200</v>
-      </c>
-      <c r="K21" t="n">
-        <v>51</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7697</v>
-      </c>
-      <c r="M21" t="n">
-        <v>29375</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-145262</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10004</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2184</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>38</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8348</v>
-      </c>
-      <c r="M22" t="n">
-        <v>31293</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-99396</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7885</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="E23" t="n">
-        <v>658</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>152</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I23" t="n">
-        <v>41</v>
-      </c>
-      <c r="J23" t="n">
-        <v>30</v>
-      </c>
-      <c r="K23" t="n">
-        <v>276</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1285</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8973</v>
-      </c>
-      <c r="N23" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3534</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>-51</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-1683</v>
-      </c>
-      <c r="H24" t="n">
-        <v>716</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J24" t="n">
-        <v>151</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2785</v>
-      </c>
-      <c r="L24" t="n">
-        <v>12744</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106311</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260323.xlsx
+++ b/outputs/monitor_xlsx/20260323.xlsx
@@ -544,10 +544,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.47%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-1.39%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-3.64%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.69%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+1.34%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-2.35%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-10.36%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-839.23億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-411.38億</t>
@@ -807,7 +769,6 @@
           <t>105.35億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>22.33億</t>
@@ -818,8 +779,6 @@
           <t>111.64億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>133.74%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-1044.99億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>10096口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11622口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>48.57億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-5.91億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1753,7 +1696,7 @@
         <v>658</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>152</v>
@@ -1997,6 +1940,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>325</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>758</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" t="n">
+        <v>73</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8242</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43026</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22118</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260323.xlsx
+++ b/outputs/monitor_xlsx/20260323.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>74.25</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-2.17</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>233385</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-87814</v>
       </c>
       <c r="H4" t="n">
-        <v>-141639</v>
+        <v>-229453</v>
       </c>
       <c r="I4" t="n">
         <v>3100</v>
       </c>
       <c r="J4" t="n">
-        <v>6550</v>
+        <v>9650</v>
       </c>
       <c r="K4" t="n">
         <v>94383</v>
@@ -1274,11 +1273,14 @@
         <v>14088</v>
       </c>
       <c r="M4" t="n">
-        <v>51612</v>
+        <v>65700</v>
       </c>
       <c r="N4" t="n">
         <v>-4504837</v>
       </c>
+      <c r="O4" t="n">
+        <v>-3.81</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>890</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-2.84</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>4091</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-435</v>
       </c>
       <c r="H5" t="n">
-        <v>108</v>
+        <v>-328</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>-36</v>
+        <v>-33</v>
       </c>
       <c r="K5" t="n">
         <v>139</v>
@@ -1329,11 +1331,14 @@
         <v>2950</v>
       </c>
       <c r="M5" t="n">
-        <v>11523</v>
+        <v>14473</v>
       </c>
       <c r="N5" t="n">
         <v>-78845</v>
       </c>
+      <c r="O5" t="n">
+        <v>-5.76</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1410</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-4.41</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>13897</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-2506</v>
       </c>
       <c r="H6" t="n">
-        <v>8878</v>
+        <v>6372</v>
       </c>
       <c r="I6" t="n">
         <v>324</v>
       </c>
       <c r="J6" t="n">
-        <v>-479</v>
+        <v>-154</v>
       </c>
       <c r="K6" t="n">
         <v>966</v>
@@ -1384,11 +1389,14 @@
         <v>5475</v>
       </c>
       <c r="M6" t="n">
-        <v>21799</v>
+        <v>27274</v>
       </c>
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
+      <c r="O6" t="n">
+        <v>2.55</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1810</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1.63</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>41950</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-15306</v>
       </c>
       <c r="H7" t="n">
-        <v>-29416</v>
+        <v>-44721</v>
       </c>
       <c r="I7" t="n">
         <v>1861</v>
       </c>
       <c r="J7" t="n">
-        <v>-4765</v>
+        <v>-2904</v>
       </c>
       <c r="K7" t="n">
         <v>1135</v>
@@ -1439,11 +1447,14 @@
         <v>26222</v>
       </c>
       <c r="M7" t="n">
-        <v>102385</v>
+        <v>128607</v>
       </c>
       <c r="N7" t="n">
         <v>-6483121</v>
       </c>
+      <c r="O7" t="n">
+        <v>-4.51</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1565</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3284</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-27</v>
       </c>
       <c r="H8" t="n">
-        <v>1150</v>
+        <v>1123</v>
       </c>
       <c r="I8" t="n">
         <v>115</v>
       </c>
       <c r="J8" t="n">
-        <v>226</v>
+        <v>341</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -1494,11 +1505,14 @@
         <v>2186</v>
       </c>
       <c r="M8" t="n">
-        <v>8949</v>
+        <v>11135</v>
       </c>
       <c r="N8" t="n">
         <v>-140175</v>
       </c>
+      <c r="O8" t="n">
+        <v>7.5</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1520</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-4.1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>3534</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-51</v>
       </c>
       <c r="H9" t="n">
-        <v>-1632</v>
+        <v>-1683</v>
       </c>
       <c r="I9" t="n">
         <v>716</v>
       </c>
       <c r="J9" t="n">
-        <v>1306</v>
+        <v>2022</v>
       </c>
       <c r="K9" t="n">
         <v>151</v>
@@ -1549,11 +1563,14 @@
         <v>2785</v>
       </c>
       <c r="M9" t="n">
-        <v>13423</v>
+        <v>16208</v>
       </c>
       <c r="N9" t="n">
         <v>-106311</v>
       </c>
+      <c r="O9" t="n">
+        <v>7.23</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2795</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-0.53</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3517</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-24</v>
       </c>
       <c r="H10" t="n">
-        <v>-417</v>
+        <v>-441</v>
       </c>
       <c r="I10" t="n">
         <v>112</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -1604,11 +1621,14 @@
         <v>2005</v>
       </c>
       <c r="M10" t="n">
-        <v>7691</v>
+        <v>9696</v>
       </c>
       <c r="N10" t="n">
         <v>-89580</v>
       </c>
+      <c r="O10" t="n">
+        <v>12.37</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1850</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-9.539999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>3092</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-601</v>
       </c>
       <c r="H11" t="n">
-        <v>329</v>
+        <v>-272</v>
       </c>
       <c r="I11" t="n">
         <v>229</v>
       </c>
       <c r="J11" t="n">
-        <v>44</v>
+        <v>273</v>
       </c>
       <c r="K11" t="n">
         <v>139</v>
@@ -1659,11 +1679,14 @@
         <v>4245</v>
       </c>
       <c r="M11" t="n">
-        <v>16527</v>
+        <v>20772</v>
       </c>
       <c r="N11" t="n">
         <v>-19518</v>
       </c>
+      <c r="O11" t="n">
+        <v>-4.28</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,7 +1709,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7885</v>
       </c>
       <c r="E12" s="6" t="n">
@@ -1696,7 +1719,7 @@
         <v>658</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>152</v>
@@ -1705,7 +1728,7 @@
         <v>-8</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
         <v>30</v>
@@ -1714,11 +1737,14 @@
         <v>276</v>
       </c>
       <c r="M12" t="n">
-        <v>1009</v>
+        <v>1285</v>
       </c>
       <c r="N12" t="n">
         <v>-8973</v>
       </c>
+      <c r="O12" t="n">
+        <v>36.39</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-205</v>
       </c>
       <c r="H13" t="n">
-        <v>432</v>
+        <v>227</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K13" t="n">
         <v>65</v>
@@ -1769,11 +1795,14 @@
         <v>-76</v>
       </c>
       <c r="M13" t="n">
-        <v>-616</v>
+        <v>-692</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-232</v>
       </c>
       <c r="H14" t="n">
-        <v>-4621</v>
+        <v>-4853</v>
       </c>
       <c r="I14" t="n">
         <v>167</v>
       </c>
       <c r="J14" t="n">
-        <v>-2416</v>
+        <v>-2250</v>
       </c>
       <c r="K14" t="n">
         <v>-103</v>
@@ -1824,11 +1853,14 @@
         <v>-399</v>
       </c>
       <c r="M14" t="n">
-        <v>2050</v>
+        <v>1651</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>-1620</v>
       </c>
       <c r="H15" t="n">
-        <v>-15</v>
+        <v>-1635</v>
       </c>
       <c r="I15" t="n">
         <v>1512</v>
       </c>
       <c r="J15" t="n">
-        <v>806</v>
+        <v>2318</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -1879,11 +1911,14 @@
         <v>26</v>
       </c>
       <c r="M15" t="n">
-        <v>866</v>
+        <v>892</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1906,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>44</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>70</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-6</v>
@@ -1931,11 +1969,14 @@
         <v>-104</v>
       </c>
       <c r="M16" t="n">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1953,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>325</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>-5.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>758</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-500</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>30</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>73</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8242</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>43026</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22118</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.79</v>
+      <c r="O17" t="n">
+        <v>3.04</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260323.xlsx
+++ b/outputs/monitor_xlsx/20260323.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1719,7 +1719,7 @@
         <v>658</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>152</v>
@@ -2034,6 +2034,165 @@
       </c>
       <c r="O17" t="n">
         <v>3.04</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7225</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-1675</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-5045</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-699</v>
+      </c>
+      <c r="K18" t="n">
+        <v>705</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6160</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30141</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400976</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>499</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-9.93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8936</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-245</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6992</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-225</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1110</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32909</v>
+      </c>
+      <c r="M19" t="n">
+        <v>171928</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393879</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>534</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15708</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>1878</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-6768</v>
+      </c>
+      <c r="I20" t="n">
+        <v>170</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1992</v>
+      </c>
+      <c r="K20" t="n">
+        <v>608</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9443</v>
+      </c>
+      <c r="M20" t="n">
+        <v>52377</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161137</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.28</v>
       </c>
     </row>
   </sheetData>
